--- a/Context Data/CME Attendance Report SBIRT Zoom 2-11-2022.xlsx
+++ b/Context Data/CME Attendance Report SBIRT Zoom 2-11-2022.xlsx
@@ -2815,10 +2815,10 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100506302491B512543A7F80B3AD4763AF3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="eaf80efeca9cbd8e6abe1fd2c1bf24e2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="613fbc36-a53f-4b50-a249-16232ea28364" xmlns:ns3="0b5a712f-c0ca-4ddc-98b4-eb0740769fde" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b6c035909ea78a7240c429bd766c007" ns2:_="" ns3:_="">
-    <xsd:import namespace="613fbc36-a53f-4b50-a249-16232ea28364"/>
-    <xsd:import namespace="0b5a712f-c0ca-4ddc-98b4-eb0740769fde"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D9425BFD98FC2C4FA733E6DF42251950" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e61b075310ac2dd66d1776635675bb6f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fff059bb-b667-4476-9a60-571bf927bc8d" xmlns:ns3="dfeb989f-b0e3-4d2a-bb54-484d4dc74e52" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="37a8add6a824d406915a1997c07ee314" ns2:_="" ns3:_="">
+    <xsd:import namespace="fff059bb-b667-4476-9a60-571bf927bc8d"/>
+    <xsd:import namespace="dfeb989f-b0e3-4d2a-bb54-484d4dc74e52"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -2827,16 +2827,14 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2844,7 +2842,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="613fbc36-a53f-4b50-a249-16232ea28364" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fff059bb-b667-4476-9a60-571bf927bc8d" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -2857,60 +2855,50 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="138fa7a7-b18c-4352-a067-90bbe88a6642" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="138fa7a7-b18c-4352-a067-90bbe88a6642" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0b5a712f-c0ca-4ddc-98b4-eb0740769fde" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dfeb989f-b0e3-4d2a-bb54-484d4dc74e52" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{2a6cdb3a-e745-4e03-9c4f-b414c4425e84}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0b5a712f-c0ca-4ddc-98b4-eb0740769fde">
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ed739e65-922e-410f-a9ab-5ebaf558b2b6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="dfeb989f-b0e3-4d2a-bb54-484d4dc74e52">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -3024,8 +3012,8 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="0b5a712f-c0ca-4ddc-98b4-eb0740769fde" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="613fbc36-a53f-4b50-a249-16232ea28364">
+    <TaxCatchAll xmlns="dfeb989f-b0e3-4d2a-bb54-484d4dc74e52" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fff059bb-b667-4476-9a60-571bf927bc8d">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
@@ -3041,22 +3029,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07973AB-88BC-44FF-BB36-F2C49D2B5D64}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="613fbc36-a53f-4b50-a249-16232ea28364"/>
-    <ds:schemaRef ds:uri="0b5a712f-c0ca-4ddc-98b4-eb0740769fde"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A1201E-AE60-4A8D-B284-76AC90A98FA4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
